--- a/data/trans_dic/P32-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,9</t>
+          <t>1,37; 8,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 31,71</t>
+          <t>17,86; 31,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 22,09</t>
+          <t>10,02; 22,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,84</t>
+          <t>1,82; 10,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,73</t>
+          <t>1,69; 13,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,62</t>
+          <t>4,28; 14,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,47</t>
+          <t>1,32; 6,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,93; 22,24</t>
+          <t>13,15; 22,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,48</t>
+          <t>9,2; 17,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,13</t>
+          <t>1,11; 6,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,04</t>
+          <t>3,46; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,81</t>
+          <t>5,58; 12,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,68</t>
+          <t>0,38; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,78</t>
+          <t>0,36; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,35</t>
+          <t>0,66; 6,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,68</t>
+          <t>2,69; 7,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,54</t>
+          <t>4,58; 9,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,04</t>
+          <t>0,31; 2,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,22</t>
+          <t>0,33; 3,36</t>
         </is>
       </c>
     </row>
@@ -997,42 +997,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,85</t>
+          <t>0,47; 4,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,3</t>
+          <t>0,85; 4,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 15,92</t>
+          <t>6,3; 15,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,02</t>
+          <t>0,67; 6,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,25</t>
+          <t>0,58; 3,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,39</t>
+          <t>0,62; 3,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,45</t>
+          <t>4,86; 11,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,6</t>
+          <t>2,35; 8,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,55</t>
+          <t>1,91; 8,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,57</t>
+          <t>1,92; 7,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,08</t>
+          <t>2,01; 8,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,0</t>
+          <t>0,9; 8,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,98</t>
+          <t>2,52; 6,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,69</t>
+          <t>1,73; 6,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,64</t>
+          <t>1,73; 5,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,5</t>
+          <t>1,46; 5,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,27</t>
+          <t>0,86; 7,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 14,33</t>
+          <t>4,64; 15,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 7,62</t>
+          <t>1,01; 8,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,57</t>
+          <t>0,0; 16,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,85</t>
+          <t>0,64; 7,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,07</t>
+          <t>3,39; 11,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,07</t>
+          <t>0,73; 6,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,88</t>
+          <t>0,89; 6,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,69</t>
+          <t>1,26; 7,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,65</t>
+          <t>1,0; 5,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,85</t>
+          <t>2,97; 9,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 5,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,38</t>
+          <t>0,76; 6,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,33</t>
+          <t>0,92; 4,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,35</t>
+          <t>1,18; 5,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,29</t>
+          <t>0,97; 4,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,34</t>
+          <t>2,48; 7,1</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,95</t>
+          <t>0,63; 4,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,4</t>
+          <t>3,16; 7,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,48</t>
+          <t>6,68; 13,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 19,44</t>
+          <t>9,64; 20,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,94</t>
+          <t>0,46; 4,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,79</t>
+          <t>4,49; 11,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,03</t>
+          <t>0,72; 8,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,66</t>
+          <t>0,44; 2,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,43</t>
+          <t>2,38; 5,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,37</t>
+          <t>6,71; 11,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,92</t>
+          <t>3,7; 12,6</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,25</t>
+          <t>0,72; 3,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,54</t>
+          <t>2,45; 6,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,11</t>
+          <t>1,75; 5,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,63</t>
+          <t>0,97; 4,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,99</t>
+          <t>0,51; 4,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,89</t>
+          <t>0,38; 4,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,43</t>
+          <t>0,99; 8,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,55</t>
+          <t>0,7; 2,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,36</t>
+          <t>2,2; 5,3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,04</t>
+          <t>1,46; 3,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,44</t>
+          <t>1,27; 4,54</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,7</t>
+          <t>2,07; 3,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,92</t>
+          <t>5,66; 7,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,45</t>
+          <t>4,28; 6,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,64</t>
+          <t>4,94; 7,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,54</t>
+          <t>0,79; 2,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,34</t>
+          <t>1,32; 3,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,51</t>
+          <t>2,32; 4,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,67</t>
+          <t>1,22; 3,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,96</t>
+          <t>1,83; 3,0</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,13</t>
+          <t>4,33; 6,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,39</t>
+          <t>3,73; 5,27</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,76</t>
+          <t>3,58; 5,78</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1907; 11545</t>
+          <t>2002; 12454</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32466; 55601</t>
+          <t>31306; 55914</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18905; 39470</t>
+          <t>17903; 39998</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3177; 19501</t>
+          <t>3274; 18439</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7442</t>
+          <t>0; 5997</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1844; 16008</t>
+          <t>1840; 14657</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3791; 16260</t>
+          <t>4454; 15286</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3744; 14216</t>
+          <t>2896; 14752</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36712; 63169</t>
+          <t>37352; 65189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25939; 49429</t>
+          <t>26016; 50234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3206; 19286</t>
+          <t>3011; 18808</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7181; 20687</t>
+          <t>7907; 22669</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18182; 39737</t>
+          <t>17317; 39252</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017; 9840</t>
+          <t>1017; 9135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>885; 12170</t>
+          <t>928; 13039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5025</t>
+          <t>0; 4448</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>993; 9607</t>
+          <t>1001; 9739</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6309</t>
+          <t>0; 6517</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3064</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7986; 23169</t>
+          <t>8102; 22541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20981; 44021</t>
+          <t>21140; 44602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1131; 11255</t>
+          <t>1132; 10403</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1279; 11944</t>
+          <t>1219; 12442</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 5027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1027; 9826</t>
+          <t>955; 8949</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1857; 10829</t>
+          <t>1725; 9468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11941; 29484</t>
+          <t>11659; 28030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4925</t>
+          <t>0; 5041</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4206</t>
+          <t>0; 3942</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>606; 5433</t>
+          <t>607; 5887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4999</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1882; 10631</t>
+          <t>1886; 10539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1821; 11074</t>
+          <t>2016; 11838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14193; 31554</t>
+          <t>13392; 30572</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5501; 20458</t>
+          <t>5591; 20380</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3094; 18170</t>
+          <t>3636; 16132</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4323; 17679</t>
+          <t>4482; 17037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3815; 16175</t>
+          <t>3586; 15696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1180; 11778</t>
+          <t>1174; 11215</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6446</t>
+          <t>0; 5595</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9532</t>
+          <t>0; 8907</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3021</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9436; 25740</t>
+          <t>9304; 25792</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4839; 18575</t>
+          <t>4800; 17943</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6339; 21664</t>
+          <t>6639; 21692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4352; 16647</t>
+          <t>4419; 16912</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>812; 7044</t>
+          <t>831; 6959</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5447; 18378</t>
+          <t>5945; 19861</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>922; 6877</t>
+          <t>909; 7606</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1267</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8143</t>
+          <t>0; 7503</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4513</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1746</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2375</t>
+          <t>0; 2046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933; 11247</t>
+          <t>923; 10566</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6564; 20179</t>
+          <t>6180; 21022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>937; 7752</t>
+          <t>933; 7666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2437</t>
+          <t>0; 2490</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1031; 11431</t>
+          <t>1736; 12406</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2875; 14176</t>
+          <t>2320; 12927</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1875; 10675</t>
+          <t>1885; 10592</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5346; 16256</t>
+          <t>4902; 16056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6117</t>
+          <t>0; 6091</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4803</t>
+          <t>0; 5189</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6113</t>
+          <t>0; 6686</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>540; 6148</t>
+          <t>729; 6260</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2778; 13249</t>
+          <t>2821; 14025</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3049; 14893</t>
+          <t>3283; 15023</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2868; 12592</t>
+          <t>2841; 14226</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7099; 19190</t>
+          <t>6482; 18566</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1881; 11463</t>
+          <t>1824; 12761</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11653; 29421</t>
+          <t>12559; 31604</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26224; 51299</t>
+          <t>25433; 50940</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28774; 59851</t>
+          <t>29682; 62744</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>972; 8451</t>
+          <t>986; 9008</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11169; 27949</t>
+          <t>11628; 28963</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3393; 36129</t>
+          <t>2867; 35268</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1769; 11233</t>
+          <t>1847; 11967</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14436; 33253</t>
+          <t>14562; 34855</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41016; 72703</t>
+          <t>42925; 70965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23688; 91528</t>
+          <t>26236; 89247</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3550; 16037</t>
+          <t>3526; 15895</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10640; 29600</t>
+          <t>11085; 30145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8203; 23308</t>
+          <t>7997; 23039</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2790; 12839</t>
+          <t>2684; 12351</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6811</t>
+          <t>0; 6481</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1061; 10766</t>
+          <t>1102; 9929</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1113; 10322</t>
+          <t>1001; 11165</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>734; 8419</t>
+          <t>990; 8664</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4811; 18691</t>
+          <t>5156; 18748</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14793; 35830</t>
+          <t>14737; 35462</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11256; 29124</t>
+          <t>10532; 28365</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4946; 16739</t>
+          <t>4785; 17143</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>39191; 69535</t>
+          <t>38924; 66093</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>114844; 161660</t>
+          <t>115514; 162242</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86191; 129082</t>
+          <t>85564; 128607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76577; 120635</t>
+          <t>77979; 121734</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6959; 22689</t>
+          <t>7108; 22856</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14266; 35088</t>
+          <t>13863; 34593</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27059; 51661</t>
+          <t>26546; 51518</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>12219; 37688</t>
+          <t>12493; 37468</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50238; 82102</t>
+          <t>50788; 83364</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136494; 189385</t>
+          <t>133873; 187440</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118964; 169567</t>
+          <t>117227; 165883</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93260; 150209</t>
+          <t>93197; 150627</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,52</t>
+          <t>1,34; 8,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 31,89</t>
+          <t>18,07; 31,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 22,39</t>
+          <t>10,16; 22,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,25</t>
+          <t>1,54; 8,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,16</t>
+          <t>0,0; 9,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,49</t>
+          <t>1,68; 15,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,68</t>
+          <t>3,58; 15,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,72</t>
+          <t>1,52; 6,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 22,96</t>
+          <t>12,55; 22,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 17,76</t>
+          <t>8,89; 17,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,95</t>
+          <t>1,1; 5,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,91</t>
+          <t>3,09; 9,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,66</t>
+          <t>5,74; 12,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,41</t>
+          <t>0,38; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,12</t>
+          <t>0,36; 4,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,43</t>
+          <t>0,66; 6,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,47</t>
+          <t>2,69; 7,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,66</t>
+          <t>4,68; 9,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,81</t>
+          <t>0,31; 2,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,36</t>
+          <t>0,34; 3,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,42</t>
+          <t>0,47; 4,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,64</t>
+          <t>0,84; 5,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,14</t>
+          <t>8,34; 18,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,52</t>
+          <t>0,68; 5,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,22</t>
+          <t>0,58; 3,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,62</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,1</t>
+          <t>5,95; 13,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,57</t>
+          <t>2,33; 8,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,48</t>
+          <t>2,04; 8,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,3</t>
+          <t>1,97; 7,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,81</t>
+          <t>1,9; 8,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,57</t>
+          <t>0,89; 9,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,99</t>
+          <t>2,35; 6,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,47</t>
+          <t>1,69; 6,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,64</t>
+          <t>1,72; 5,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,59</t>
+          <t>1,39; 5,7</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,18</t>
+          <t>0,84; 7,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 15,49</t>
+          <t>4,6; 15,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,42</t>
+          <t>1,03; 8,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,19</t>
+          <t>0,0; 17,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,69</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,38</t>
+          <t>0,63; 7,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,53</t>
+          <t>3,78; 11,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,0</t>
+          <t>0,72; 6,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,39</t>
+          <t>0,55; 6,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,02</t>
+          <t>1,31; 7,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,6</t>
+          <t>0,98; 5,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 9,73</t>
+          <t>3,15; 9,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,49</t>
+          <t>0,63; 7,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,58</t>
+          <t>0,94; 4,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,4</t>
+          <t>1,05; 4,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,84</t>
+          <t>0,97; 4,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,1</t>
+          <t>2,69; 7,28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,4</t>
+          <t>0,63; 4,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,95</t>
+          <t>2,95; 8,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,39</t>
+          <t>6,58; 13,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,64; 20,38</t>
+          <t>10,03; 19,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,2</t>
+          <t>0,46; 4,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,18</t>
+          <t>4,43; 10,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,81</t>
+          <t>5,17; 13,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,83</t>
+          <t>0,42; 2,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,7</t>
+          <t>2,36; 5,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,1</t>
+          <t>6,67; 11,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,6</t>
+          <t>9,07; 15,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,22</t>
+          <t>0,72; 3,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,66</t>
+          <t>2,5; 6,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,05</t>
+          <t>1,72; 5,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,45</t>
+          <t>0,96; 4,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,6</t>
+          <t>0,49; 4,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,21</t>
+          <t>0,42; 3,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,68</t>
+          <t>0,7; 7,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,56</t>
+          <t>0,7; 2,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,3</t>
+          <t>2,22; 5,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,93</t>
+          <t>1,61; 3,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,54</t>
+          <t>1,32; 4,72</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,51</t>
+          <t>2,08; 3,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,95</t>
+          <t>5,61; 8,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,43</t>
+          <t>4,32; 6,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,71</t>
+          <t>5,2; 8,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,8; 2,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,29</t>
+          <t>1,31; 3,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,49</t>
+          <t>2,39; 4,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,65</t>
+          <t>2,4; 5,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,0</t>
+          <t>1,8; 2,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,06</t>
+          <t>4,4; 6,01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,27</t>
+          <t>3,84; 5,34</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,78</t>
+          <t>4,59; 6,54</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>6867</t>
         </is>
       </c>
     </row>
@@ -2209,37 +2209,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2002; 12454</t>
+          <t>1957; 11699</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31306; 55914</t>
+          <t>31686; 55222</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17903; 39998</t>
+          <t>18144; 39798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3274; 18439</t>
+          <t>2621; 14904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5997</t>
+          <t>0; 6866</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1840; 14657</t>
+          <t>1821; 16708</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4454; 15286</t>
+          <t>3729; 15690</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2896; 14752</t>
+          <t>3339; 14474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37352; 65189</t>
+          <t>35651; 64626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26016; 50234</t>
+          <t>25152; 49812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3011; 18808</t>
+          <t>2942; 15393</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>602</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4776</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7907; 22669</t>
+          <t>7065; 20613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17317; 39252</t>
+          <t>17792; 37926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017; 9135</t>
+          <t>1015; 9531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>928; 13039</t>
+          <t>933; 12565</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4448</t>
+          <t>0; 5843</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1001; 9739</t>
+          <t>998; 9955</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6517</t>
+          <t>0; 4510</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3007</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8102; 22541</t>
+          <t>8122; 23532</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21140; 44602</t>
+          <t>21618; 45501</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1132; 10403</t>
+          <t>1135; 10904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1219; 12442</t>
+          <t>1283; 13480</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>25915</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5027</t>
+          <t>0; 5914</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>955; 8949</t>
+          <t>951; 9373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1725; 9468</t>
+          <t>1724; 10200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11659; 28030</t>
+          <t>15617; 34057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5041</t>
+          <t>0; 5019</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 4680</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>607; 5887</t>
+          <t>606; 5309</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 5662</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1886; 10539</t>
+          <t>1895; 11467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2016; 11838</t>
+          <t>1966; 11119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13392; 30572</t>
+          <t>16444; 37242</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9614</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5591; 20380</t>
+          <t>5545; 19605</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3636; 16132</t>
+          <t>3873; 16878</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4482; 17037</t>
+          <t>4602; 17873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3586; 15696</t>
+          <t>3857; 16772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1174; 11215</t>
+          <t>1172; 11972</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5595</t>
+          <t>0; 6030</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 8907</t>
+          <t>0; 8748</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9304; 25792</t>
+          <t>8668; 24899</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4800; 17943</t>
+          <t>4689; 18549</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6639; 21692</t>
+          <t>6617; 21649</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4419; 16912</t>
+          <t>4755; 19491</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>831; 6959</t>
+          <t>816; 7200</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5945; 19861</t>
+          <t>5892; 19266</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>909; 7606</t>
+          <t>933; 7595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7503</t>
+          <t>0; 8065</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4700</t>
+          <t>0; 5224</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>923; 10566</t>
+          <t>907; 10599</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6180; 21022</t>
+          <t>6883; 20416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933; 7666</t>
+          <t>922; 8536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2490</t>
+          <t>0; 2472</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12046</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1736; 12406</t>
+          <t>1059; 12509</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2320; 12927</t>
+          <t>2416; 13386</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1885; 10592</t>
+          <t>1853; 10760</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4902; 16056</t>
+          <t>5138; 15827</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6091</t>
+          <t>0; 5975</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5189</t>
+          <t>0; 4714</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6686</t>
+          <t>0; 5788</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>729; 6260</t>
+          <t>615; 7070</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2821; 14025</t>
+          <t>2863; 14554</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3283; 15023</t>
+          <t>2927; 13478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2841; 14226</t>
+          <t>2863; 12744</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6482; 18566</t>
+          <t>7038; 19018</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41876</t>
+          <t>49594</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56467</t>
+          <t>69949</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1824; 12761</t>
+          <t>1839; 12962</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12559; 31604</t>
+          <t>11733; 31982</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25433; 50940</t>
+          <t>25030; 51156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29682; 62744</t>
+          <t>35064; 66542</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>986; 9008</t>
+          <t>977; 8960</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11628; 28963</t>
+          <t>11465; 27564</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2867; 35268</t>
+          <t>12145; 32133</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1847; 11967</t>
+          <t>1783; 12166</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14562; 34855</t>
+          <t>14423; 35237</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42925; 70965</t>
+          <t>42666; 71796</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26236; 89247</t>
+          <t>53033; 91218</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>10797</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3526; 15895</t>
+          <t>3536; 16363</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11085; 30145</t>
+          <t>11326; 31451</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7997; 23039</t>
+          <t>7838; 23703</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2684; 12351</t>
+          <t>3004; 14140</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6481</t>
+          <t>0; 7803</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1102; 9929</t>
+          <t>1057; 10317</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1001; 11165</t>
+          <t>1121; 10370</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>990; 8664</t>
+          <t>809; 9001</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5156; 18748</t>
+          <t>5105; 17775</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14737; 35462</t>
+          <t>14841; 35641</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10532; 28365</t>
+          <t>11651; 27934</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4785; 17143</t>
+          <t>5647; 20260</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>38924; 66093</t>
+          <t>39033; 67920</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>115514; 162242</t>
+          <t>114463; 163599</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85564; 128607</t>
+          <t>86421; 127534</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>77979; 121734</t>
+          <t>87427; 134739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7108; 22856</t>
+          <t>7166; 22250</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13863; 34593</t>
+          <t>13739; 35819</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26546; 51518</t>
+          <t>27421; 51923</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>12493; 37468</t>
+          <t>21744; 45524</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50788; 83364</t>
+          <t>49996; 81576</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133873; 187440</t>
+          <t>135889; 185844</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>117227; 165883</t>
+          <t>120909; 168154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93197; 150627</t>
+          <t>118684; 169199</t>
         </is>
       </c>
     </row>
